--- a/metadata/plate_metadata/20260324_cep290_18hpf_24hpf_plate02_well_metadata.xlsx
+++ b/metadata/plate_metadata/20260324_cep290_18hpf_24hpf_plate02_well_metadata.xlsx
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
     </row>
@@ -1682,18 +1682,18 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I5" s="17" t="n"/>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
@@ -1750,13 +1750,13 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I6" s="17" t="n"/>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
